--- a/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
+++ b/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
+++ b/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
+++ b/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
+++ b/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
+++ b/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6399" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6399" uniqueCount="778">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,10 +269,10 @@
 </t>
   </si>
   <si>
-    <t>Measurements and simple assertions</t>
-  </si>
-  <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+    <t>通用檢驗檢查結果或發現的測量和簡單聲明</t>
+  </si>
+  <si>
+    <t>關於患者的通用檢驗檢查結果測量和簡單聲明，包括由設備或醫護人員觀察到的發現。</t>
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
@@ -346,10 +346,10 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+    <t>創建此內容所依據的一組規則</t>
+  </si>
+  <si>
+    <t>構建 resource 時遵循的一系列規則的參照，在處理內容時必須理解這些規則。通常這是對 IG 所定義之特殊規則及其他 profiles 的參照。</t>
   </si>
   <si>
     <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -520,10 +520,10 @@
 </t>
   </si>
   <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+    <t>檢驗檢查的依據</t>
+  </si>
+  <si>
+    <t>產生此檢驗檢查的計畫或請求。</t>
   </si>
   <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
@@ -549,10 +549,10 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+    <t>作為較大項目的一部分</t>
+  </si>
+  <si>
+    <t>表示此檢驗檢查是其他資源的一部分，例如：用藥給藥、調劑、用藥聲明、處置、免疫接種或影像檢查。</t>
   </si>
   <si>
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
@@ -573,7 +573,7 @@
     <t>registered | preliminary | final | amended +</t>
   </si>
   <si>
-    <t>The status of the result value.</t>
+    <t>該項檢驗檢查的狀態。</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -613,10 +613,10 @@
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
+    <t>檢驗檢查的分類</t>
+  </si>
+  <si>
+    <t>檢驗檢查的分類。</t>
   </si>
   <si>
     <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -628,7 +628,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -654,7 +654,13 @@
 </t>
   </si>
   <si>
-    <t>此slice綁定的值集之綁定強度雖為最高強度「要求使用(Requird)」，但因slice之特性，其不會限制僅能填此值集中的代碼，故在實作時也可使用其他值集的代碼。</t>
+    <t>臺灣核心分類</t>
+  </si>
+  <si>
+    <t>臺灣核心檢驗檢查分類。</t>
+  </si>
+  <si>
+    <t>此 slice 綁定的值集之綁定強度雖為最高強度「要求使用 (Requird)」，但因 slice 之特性，其不會限制僅能填此值集中的代碼，故在實作時也可使用其他值集的代碼。</t>
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/category-code-tw</t>
@@ -917,13 +923,13 @@
 </t>
   </si>
   <si>
-    <t>概念（Concept）— 參照一個專門術語或只是文字表述</t>
-  </si>
-  <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>檢驗檢查類型</t>
+  </si>
+  <si>
+    <t>描述該檢驗檢查所測量的內容</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
@@ -935,14 +941,22 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -979,12 +993,6 @@
     <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
@@ -1100,7 +1108,7 @@
     <t>量測對象</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>檢驗檢查關注的主體 (如患者、群組、設備或位置)。</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
@@ -1210,7 +1218,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1221,9 +1229,6 @@
   </si>
   <si>
     <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1240,10 +1245,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>與此檢驗檢查相關的就醫事件</t>
+  </si>
+  <si>
+    <t>此檢驗檢查是在哪個就醫情境產生的。</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1275,10 +1280,10 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+    <t>檢驗檢查的時間或時段</t>
+  </si>
+  <si>
+    <t>檢驗檢查進行的時間點或時間段。</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
@@ -1334,7 +1339,7 @@
     <t>量測人員</t>
   </si>
   <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
+    <t>執行或負責檢驗檢查的人員。</t>
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
@@ -1376,10 +1381,10 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+    <t>檢驗檢查的結果值</t>
+  </si>
+  <si>
+    <t>檢驗檢查或觀察的實際結果。</t>
   </si>
   <si>
     <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1502,7 +1507,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1534,7 +1539,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1633,10 +1638,10 @@
 </t>
   </si>
   <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
+    <t>檢驗檢查的檢體</t>
+  </si>
+  <si>
+    <t>進行檢驗檢查的檢體。</t>
   </si>
   <si>
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
@@ -1657,7 +1662,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1737,7 +1742,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1787,7 +1792,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1823,7 +1828,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1864,10 +1869,10 @@
 </t>
   </si>
   <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+    <t>包含的相關檢驗檢查</t>
+  </si>
+  <si>
+    <t>與此檢驗檢查相關聯的其他檢驗檢查或問卷回應。</t>
   </si>
   <si>
     <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
@@ -1886,10 +1891,10 @@
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+    <t>觀察來源或依據</t>
+  </si>
+  <si>
+    <t>用於獲取此觀察結果的參考資源，如：來源觀察、文件引用、問卷回應等。</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
@@ -1950,16 +1955,13 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -1968,6 +1970,9 @@
   </si>
   <si>
     <t>Actual component result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -2762,7 +2767,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="114.32421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="116.8203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.0625" customWidth="true" bestFit="true"/>
@@ -4624,10 +4629,10 @@
         <v>203</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>193</v>
@@ -4661,10 +4666,10 @@
         <v>181</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -4717,10 +4722,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4743,13 +4748,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4800,7 +4805,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4824,7 +4829,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4835,10 +4840,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4867,7 +4872,7 @@
         <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>141</v>
@@ -4908,10 +4913,10 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4920,7 +4925,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4944,7 +4949,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4955,10 +4960,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4981,19 +4986,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -5042,7 +5047,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -5063,10 +5068,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -5077,10 +5082,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5103,13 +5108,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5160,7 +5165,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -5184,7 +5189,7 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -5195,10 +5200,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5227,7 +5232,7 @@
         <v>139</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>141</v>
@@ -5268,10 +5273,10 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
@@ -5280,7 +5285,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5304,7 +5309,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -5315,10 +5320,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5344,16 +5349,16 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -5363,7 +5368,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -5402,7 +5407,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5423,10 +5428,10 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -5437,10 +5442,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5463,16 +5468,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5522,7 +5527,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5543,10 +5548,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -5557,10 +5562,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5586,14 +5591,14 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5603,7 +5608,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -5642,7 +5647,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5663,10 +5668,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5677,10 +5682,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5703,17 +5708,17 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5723,7 +5728,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -5762,7 +5767,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5783,10 +5788,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5797,10 +5802,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5823,19 +5828,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5884,7 +5889,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5905,10 +5910,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5919,10 +5924,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5945,19 +5950,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -6006,7 +6011,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -6027,10 +6032,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -6041,14 +6046,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -6064,22 +6069,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -6107,10 +6112,10 @@
         <v>116</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -6128,7 +6133,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -6137,36 +6142,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>299</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6189,13 +6194,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6246,7 +6251,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6270,7 +6275,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -6281,10 +6286,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6310,10 +6315,10 @@
         <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6352,10 +6357,10 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
@@ -6364,7 +6369,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6399,10 +6404,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6422,22 +6427,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -6486,7 +6491,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6495,7 +6500,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -6507,10 +6512,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>310</v>
+        <v>229</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>311</v>
+        <v>230</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6521,10 +6526,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6547,13 +6552,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6604,7 +6609,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6628,7 +6633,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6639,10 +6644,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6668,13 +6673,13 @@
         <v>138</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6712,10 +6717,10 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
@@ -6724,7 +6729,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6759,10 +6764,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6788,16 +6793,16 @@
         <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6807,7 +6812,7 @@
         <v>20</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>20</v>
@@ -6846,7 +6851,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6867,10 +6872,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6881,10 +6886,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6907,16 +6912,16 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6966,7 +6971,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6987,10 +6992,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -7001,10 +7006,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7030,14 +7035,14 @@
         <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -7047,7 +7052,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -7086,7 +7091,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -7107,10 +7112,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -7121,10 +7126,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7147,17 +7152,17 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -7167,7 +7172,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -7206,7 +7211,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7227,10 +7232,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -7241,10 +7246,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7267,19 +7272,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -7328,7 +7333,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7349,10 +7354,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -7363,10 +7368,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7389,19 +7394,19 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7450,7 +7455,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7471,10 +7476,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7485,10 +7490,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7511,19 +7516,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7572,7 +7577,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7587,19 +7592,19 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -7607,10 +7612,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7633,13 +7638,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7690,7 +7695,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7714,7 +7719,7 @@
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7725,10 +7730,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7757,7 +7762,7 @@
         <v>139</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>141</v>
@@ -7798,10 +7803,10 @@
         <v>20</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>20</v>
@@ -7810,7 +7815,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7834,7 +7839,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7845,10 +7850,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7871,16 +7876,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7930,7 +7935,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7939,7 +7944,7 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
@@ -7965,10 +7970,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7994,13 +7999,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8026,13 +8031,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -8050,7 +8055,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8085,10 +8090,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8114,13 +8119,13 @@
         <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8170,7 +8175,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8194,7 +8199,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -8205,10 +8210,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8231,16 +8236,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8290,7 +8295,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8325,10 +8330,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8351,16 +8356,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8410,7 +8415,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8431,13 +8436,13 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>20</v>
@@ -8445,14 +8450,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8471,19 +8476,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8532,7 +8537,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8547,19 +8552,19 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>20</v>
@@ -8567,14 +8572,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8593,19 +8598,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8654,7 +8659,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8669,19 +8674,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -8689,10 +8694,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8715,16 +8720,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8774,7 +8779,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8795,13 +8800,13 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>20</v>
@@ -8809,10 +8814,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8835,17 +8840,17 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8894,7 +8899,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8909,19 +8914,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8929,10 +8934,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8955,13 +8960,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9012,7 +9017,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9036,7 +9041,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -9047,10 +9052,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9079,7 +9084,7 @@
         <v>139</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>141</v>
@@ -9120,10 +9125,10 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
@@ -9132,7 +9137,7 @@
         <v>198</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9156,7 +9161,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -9167,10 +9172,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9193,16 +9198,16 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9252,7 +9257,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9261,7 +9266,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -9287,10 +9292,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9316,13 +9321,13 @@
         <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9348,13 +9353,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -9372,7 +9377,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9407,10 +9412,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9436,13 +9441,13 @@
         <v>150</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9492,7 +9497,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9516,7 +9521,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9527,10 +9532,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9553,16 +9558,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9612,7 +9617,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9647,10 +9652,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9676,16 +9681,16 @@
         <v>203</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9722,17 +9727,17 @@
         <v>20</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9741,7 +9746,7 @@
         <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>104</v>
@@ -9750,30 +9755,30 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>20</v>
@@ -9798,16 +9803,16 @@
         <v>203</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9856,7 +9861,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9865,7 +9870,7 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9874,27 +9879,27 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9917,13 +9922,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9974,7 +9979,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9998,7 +10003,7 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -10009,10 +10014,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10041,7 +10046,7 @@
         <v>139</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>141</v>
@@ -10082,10 +10087,10 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
@@ -10094,7 +10099,7 @@
         <v>198</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10118,7 +10123,7 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -10129,10 +10134,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10155,19 +10160,19 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -10216,7 +10221,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10237,10 +10242,10 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -10251,10 +10256,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10277,13 +10282,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10334,7 +10339,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10358,7 +10363,7 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -10369,10 +10374,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10401,7 +10406,7 @@
         <v>139</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>141</v>
@@ -10442,10 +10447,10 @@
         <v>20</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>20</v>
@@ -10454,7 +10459,7 @@
         <v>198</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10478,7 +10483,7 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10489,10 +10494,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10518,16 +10523,16 @@
         <v>106</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -10576,7 +10581,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10597,10 +10602,10 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10611,10 +10616,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10637,16 +10642,16 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10696,7 +10701,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10717,10 +10722,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10731,10 +10736,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10760,14 +10765,14 @@
         <v>112</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10816,7 +10821,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10837,10 +10842,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10851,10 +10856,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10877,17 +10882,17 @@
         <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10936,7 +10941,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10957,10 +10962,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10971,10 +10976,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10997,19 +11002,19 @@
         <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -11058,7 +11063,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11079,10 +11084,10 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -11093,10 +11098,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11119,19 +11124,19 @@
         <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -11180,7 +11185,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11201,10 +11206,10 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -11215,10 +11220,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11244,16 +11249,16 @@
         <v>203</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -11278,13 +11283,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -11302,7 +11307,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11311,7 +11316,7 @@
         <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>104</v>
@@ -11326,7 +11331,7 @@
         <v>135</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -11337,14 +11342,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11366,16 +11371,16 @@
         <v>203</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -11400,13 +11405,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -11424,7 +11429,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11442,27 +11447,27 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11485,19 +11490,19 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11546,7 +11551,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11567,10 +11572,10 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11581,10 +11586,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11610,13 +11615,13 @@
         <v>203</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11642,11 +11647,11 @@
         <v>20</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -11664,7 +11669,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11682,27 +11687,27 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11728,16 +11733,16 @@
         <v>203</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11762,11 +11767,11 @@
         <v>20</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11784,7 +11789,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11805,10 +11810,10 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11819,10 +11824,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11845,16 +11850,16 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11904,7 +11909,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11922,27 +11927,27 @@
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11965,16 +11970,16 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12024,7 +12029,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12042,27 +12047,27 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12085,19 +12090,19 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -12146,7 +12151,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12158,7 +12163,7 @@
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -12167,10 +12172,10 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -12181,10 +12186,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12207,13 +12212,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12264,7 +12269,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12288,7 +12293,7 @@
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -12299,10 +12304,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12331,7 +12336,7 @@
         <v>139</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>141</v>
@@ -12384,7 +12389,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12408,7 +12413,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12419,14 +12424,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12448,10 +12453,10 @@
         <v>138</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>141</v>
@@ -12506,7 +12511,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12541,10 +12546,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12567,13 +12572,13 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12624,7 +12629,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12633,7 +12638,7 @@
         <v>92</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>104</v>
@@ -12645,10 +12650,10 @@
         <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12659,10 +12664,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12685,13 +12690,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12742,7 +12747,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12751,7 +12756,7 @@
         <v>92</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>104</v>
@@ -12763,10 +12768,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12777,10 +12782,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12806,16 +12811,16 @@
         <v>203</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12843,10 +12848,10 @@
         <v>116</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -12864,7 +12869,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12882,13 +12887,13 @@
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12899,10 +12904,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12928,16 +12933,16 @@
         <v>203</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -12962,13 +12967,13 @@
         <v>20</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
@@ -12986,7 +12991,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13004,13 +13009,13 @@
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -13021,10 +13026,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13047,17 +13052,17 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -13106,7 +13111,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13130,7 +13135,7 @@
         <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -13141,10 +13146,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13167,13 +13172,13 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13224,7 +13229,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13245,10 +13250,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -13259,10 +13264,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13285,16 +13290,16 @@
         <v>93</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13344,7 +13349,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13365,10 +13370,10 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -13379,10 +13384,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13405,16 +13410,16 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13464,7 +13469,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13485,10 +13490,10 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13499,10 +13504,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13510,7 +13515,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>81</v>
@@ -13525,19 +13530,19 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -13574,10 +13579,10 @@
         <v>20</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>20</v>
@@ -13586,7 +13591,7 @@
         <v>198</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13607,10 +13612,10 @@
         <v>20</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13621,10 +13626,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13647,13 +13652,13 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13704,7 +13709,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13728,7 +13733,7 @@
         <v>20</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13739,10 +13744,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13771,7 +13776,7 @@
         <v>139</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>141</v>
@@ -13824,7 +13829,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13848,7 +13853,7 @@
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13859,14 +13864,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13888,10 +13893,10 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>141</v>
@@ -13946,7 +13951,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13981,10 +13986,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14010,16 +14015,16 @@
         <v>203</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -14044,13 +14049,13 @@
         <v>20</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>295</v>
+        <v>623</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>20</v>
@@ -14068,7 +14073,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>92</v>
@@ -14086,16 +14091,16 @@
         <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>622</v>
+        <v>301</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>623</v>
+        <v>302</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>20</v>
@@ -14103,10 +14108,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14129,19 +14134,19 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>439</v>
+        <v>628</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -14190,7 +14195,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14208,27 +14213,27 @@
         <v>20</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14254,16 +14259,16 @@
         <v>203</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -14288,13 +14293,13 @@
         <v>20</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>20</v>
@@ -14312,7 +14317,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14321,7 +14326,7 @@
         <v>92</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>104</v>
@@ -14336,7 +14341,7 @@
         <v>135</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -14347,14 +14352,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14376,16 +14381,16 @@
         <v>203</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -14410,13 +14415,13 @@
         <v>20</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
@@ -14434,7 +14439,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14452,27 +14457,27 @@
         <v>20</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14498,16 +14503,16 @@
         <v>82</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -14556,7 +14561,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14577,10 +14582,10 @@
         <v>20</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>20</v>
@@ -14591,13 +14596,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>20</v>
@@ -14619,19 +14624,19 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -14680,7 +14685,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14701,10 +14706,10 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>
@@ -14715,10 +14720,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14741,13 +14746,13 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14798,7 +14803,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14822,7 +14827,7 @@
         <v>20</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
@@ -14833,10 +14838,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14865,7 +14870,7 @@
         <v>139</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>141</v>
@@ -14918,7 +14923,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14942,7 +14947,7 @@
         <v>20</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>20</v>
@@ -14953,14 +14958,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14982,10 +14987,10 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>141</v>
@@ -15040,7 +15045,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15075,10 +15080,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15104,16 +15109,16 @@
         <v>203</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -15138,13 +15143,13 @@
         <v>20</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>295</v>
+        <v>623</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>20</v>
@@ -15162,7 +15167,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>92</v>
@@ -15180,16 +15185,16 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>622</v>
+        <v>301</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>623</v>
+        <v>302</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>20</v>
@@ -15197,10 +15202,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15223,13 +15228,13 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15280,7 +15285,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15304,7 +15309,7 @@
         <v>20</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>20</v>
@@ -15315,10 +15320,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15347,7 +15352,7 @@
         <v>139</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>141</v>
@@ -15388,10 +15393,10 @@
         <v>20</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>20</v>
@@ -15400,7 +15405,7 @@
         <v>198</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15424,7 +15429,7 @@
         <v>20</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>20</v>
@@ -15435,10 +15440,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15461,19 +15466,19 @@
         <v>93</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>20</v>
@@ -15522,7 +15527,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15543,10 +15548,10 @@
         <v>20</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>20</v>
@@ -15557,10 +15562,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15583,13 +15588,13 @@
         <v>20</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15640,7 +15645,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15664,7 +15669,7 @@
         <v>20</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>20</v>
@@ -15675,10 +15680,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15707,7 +15712,7 @@
         <v>139</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>141</v>
@@ -15748,10 +15753,10 @@
         <v>20</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>20</v>
@@ -15760,7 +15765,7 @@
         <v>198</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15784,7 +15789,7 @@
         <v>20</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>20</v>
@@ -15795,10 +15800,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15824,16 +15829,16 @@
         <v>106</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>20</v>
@@ -15843,7 +15848,7 @@
         <v>20</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>20</v>
@@ -15882,7 +15887,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15903,10 +15908,10 @@
         <v>20</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>20</v>
@@ -15917,10 +15922,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15943,16 +15948,16 @@
         <v>93</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16002,7 +16007,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -16023,10 +16028,10 @@
         <v>20</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>20</v>
@@ -16037,10 +16042,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16066,14 +16071,14 @@
         <v>112</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -16083,7 +16088,7 @@
         <v>20</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>20</v>
@@ -16122,7 +16127,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16143,10 +16148,10 @@
         <v>20</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>20</v>
@@ -16157,10 +16162,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16183,17 +16188,17 @@
         <v>93</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -16203,7 +16208,7 @@
         <v>20</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>20</v>
@@ -16242,7 +16247,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16263,10 +16268,10 @@
         <v>20</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>20</v>
@@ -16277,10 +16282,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16303,19 +16308,19 @@
         <v>93</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>20</v>
@@ -16364,7 +16369,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16385,10 +16390,10 @@
         <v>20</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>20</v>
@@ -16399,10 +16404,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16425,19 +16430,19 @@
         <v>93</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>20</v>
@@ -16486,7 +16491,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16507,10 +16512,10 @@
         <v>20</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>20</v>
@@ -16521,10 +16526,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16547,19 +16552,19 @@
         <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>439</v>
+        <v>628</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>20</v>
@@ -16596,7 +16601,7 @@
         <v>20</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC115" s="2"/>
       <c r="AD115" t="s" s="2">
@@ -16606,7 +16611,7 @@
         <v>198</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16624,30 +16629,30 @@
         <v>20</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>20</v>
@@ -16669,19 +16674,19 @@
         <v>93</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>439</v>
+        <v>628</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -16730,7 +16735,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16748,27 +16753,27 @@
         <v>20</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16791,13 +16796,13 @@
         <v>20</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16848,7 +16853,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16872,7 +16877,7 @@
         <v>20</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>20</v>
@@ -16883,10 +16888,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16915,7 +16920,7 @@
         <v>139</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>141</v>
@@ -16956,10 +16961,10 @@
         <v>20</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>20</v>
@@ -16968,7 +16973,7 @@
         <v>198</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16992,7 +16997,7 @@
         <v>20</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>20</v>
@@ -17003,10 +17008,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17029,19 +17034,19 @@
         <v>93</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>20</v>
@@ -17090,7 +17095,7 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17111,10 +17116,10 @@
         <v>20</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>20</v>
@@ -17125,10 +17130,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17154,20 +17159,20 @@
         <v>112</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q120" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="R120" t="s" s="2">
         <v>20</v>
@@ -17191,10 +17196,10 @@
         <v>181</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>20</v>
@@ -17212,7 +17217,7 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17233,10 +17238,10 @@
         <v>20</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>20</v>
@@ -17247,10 +17252,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17273,17 +17278,17 @@
         <v>93</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>20</v>
@@ -17332,7 +17337,7 @@
         <v>20</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17353,10 +17358,10 @@
         <v>20</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>20</v>
@@ -17367,10 +17372,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17396,14 +17401,14 @@
         <v>106</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>20</v>
@@ -17413,7 +17418,7 @@
         <v>20</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>20</v>
@@ -17452,7 +17457,7 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17461,7 +17466,7 @@
         <v>92</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>104</v>
@@ -17473,10 +17478,10 @@
         <v>20</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>20</v>
@@ -17487,10 +17492,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17516,16 +17521,16 @@
         <v>112</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>20</v>
@@ -17535,7 +17540,7 @@
         <v>20</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>20</v>
@@ -17574,7 +17579,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17595,10 +17600,10 @@
         <v>20</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>20</v>
@@ -17609,10 +17614,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17638,16 +17643,16 @@
         <v>203</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>20</v>
@@ -17672,13 +17677,13 @@
         <v>20</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>20</v>
@@ -17696,7 +17701,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17705,7 +17710,7 @@
         <v>92</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>104</v>
@@ -17720,7 +17725,7 @@
         <v>135</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>20</v>
@@ -17731,14 +17736,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17760,16 +17765,16 @@
         <v>203</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -17794,13 +17799,13 @@
         <v>20</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>20</v>
@@ -17818,7 +17823,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17836,27 +17841,27 @@
         <v>20</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17882,16 +17887,16 @@
         <v>82</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>20</v>
@@ -17940,7 +17945,7 @@
         <v>20</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17961,10 +17966,10 @@
         <v>20</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>20</v>
@@ -17975,13 +17980,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>20</v>
@@ -18003,19 +18008,19 @@
         <v>93</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>20</v>
@@ -18064,7 +18069,7 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18085,10 +18090,10 @@
         <v>20</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>20</v>
@@ -18099,10 +18104,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18125,13 +18130,13 @@
         <v>20</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18182,7 +18187,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18206,7 +18211,7 @@
         <v>20</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>20</v>
@@ -18217,10 +18222,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18249,7 +18254,7 @@
         <v>139</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>141</v>
@@ -18302,7 +18307,7 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18326,7 +18331,7 @@
         <v>20</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>20</v>
@@ -18337,14 +18342,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18366,10 +18371,10 @@
         <v>138</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>141</v>
@@ -18424,7 +18429,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18459,10 +18464,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18488,16 +18493,16 @@
         <v>203</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>20</v>
@@ -18522,13 +18527,13 @@
         <v>20</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>295</v>
+        <v>623</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>20</v>
@@ -18546,7 +18551,7 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>92</v>
@@ -18564,16 +18569,16 @@
         <v>20</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>622</v>
+        <v>301</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>623</v>
+        <v>302</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>20</v>
@@ -18581,10 +18586,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18607,13 +18612,13 @@
         <v>20</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18664,7 +18669,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18688,7 +18693,7 @@
         <v>20</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>20</v>
@@ -18699,10 +18704,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18731,7 +18736,7 @@
         <v>139</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>141</v>
@@ -18772,10 +18777,10 @@
         <v>20</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>20</v>
@@ -18784,7 +18789,7 @@
         <v>198</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18808,7 +18813,7 @@
         <v>20</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>20</v>
@@ -18819,10 +18824,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18845,19 +18850,19 @@
         <v>93</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>20</v>
@@ -18906,7 +18911,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18927,10 +18932,10 @@
         <v>20</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>20</v>
@@ -18941,10 +18946,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18967,13 +18972,13 @@
         <v>20</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19024,7 +19029,7 @@
         <v>20</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19048,7 +19053,7 @@
         <v>20</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>20</v>
@@ -19059,10 +19064,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19091,7 +19096,7 @@
         <v>139</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>141</v>
@@ -19132,10 +19137,10 @@
         <v>20</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>20</v>
@@ -19144,7 +19149,7 @@
         <v>198</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19168,7 +19173,7 @@
         <v>20</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>20</v>
@@ -19179,10 +19184,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19208,16 +19213,16 @@
         <v>106</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>20</v>
@@ -19227,7 +19232,7 @@
         <v>20</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>20</v>
@@ -19266,7 +19271,7 @@
         <v>20</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19287,10 +19292,10 @@
         <v>20</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>20</v>
@@ -19301,10 +19306,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19327,16 +19332,16 @@
         <v>93</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19386,7 +19391,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19407,10 +19412,10 @@
         <v>20</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>20</v>
@@ -19421,10 +19426,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19450,14 +19455,14 @@
         <v>112</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -19467,7 +19472,7 @@
         <v>20</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>20</v>
@@ -19506,7 +19511,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19527,10 +19532,10 @@
         <v>20</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>20</v>
@@ -19541,10 +19546,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19567,17 +19572,17 @@
         <v>93</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -19587,7 +19592,7 @@
         <v>20</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>20</v>
@@ -19626,7 +19631,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19647,10 +19652,10 @@
         <v>20</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>20</v>
@@ -19661,10 +19666,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19687,19 +19692,19 @@
         <v>93</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>20</v>
@@ -19748,7 +19753,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19769,10 +19774,10 @@
         <v>20</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>20</v>
@@ -19783,10 +19788,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19809,19 +19814,19 @@
         <v>93</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -19870,7 +19875,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19891,10 +19896,10 @@
         <v>20</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>20</v>
@@ -19905,10 +19910,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19931,19 +19936,19 @@
         <v>93</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>439</v>
+        <v>628</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>20</v>
@@ -19992,7 +19997,7 @@
         <v>20</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20010,27 +20015,27 @@
         <v>20</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20056,16 +20061,16 @@
         <v>203</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>20</v>
@@ -20090,13 +20095,13 @@
         <v>20</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>20</v>
@@ -20114,7 +20119,7 @@
         <v>20</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20123,7 +20128,7 @@
         <v>92</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>104</v>
@@ -20138,7 +20143,7 @@
         <v>135</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>20</v>
@@ -20149,14 +20154,14 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -20178,16 +20183,16 @@
         <v>203</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>20</v>
@@ -20212,13 +20217,13 @@
         <v>20</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>20</v>
@@ -20236,7 +20241,7 @@
         <v>20</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20254,27 +20259,27 @@
         <v>20</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20300,16 +20305,16 @@
         <v>82</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>20</v>
@@ -20358,7 +20363,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20379,10 +20384,10 @@
         <v>20</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>20</v>
@@ -20393,13 +20398,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>20</v>
@@ -20421,19 +20426,19 @@
         <v>93</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>20</v>
@@ -20482,7 +20487,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20503,10 +20508,10 @@
         <v>20</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>20</v>
@@ -20517,10 +20522,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20543,13 +20548,13 @@
         <v>20</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20600,7 +20605,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20624,7 +20629,7 @@
         <v>20</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>20</v>
@@ -20635,10 +20640,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20667,7 +20672,7 @@
         <v>139</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>141</v>
@@ -20720,7 +20725,7 @@
         <v>20</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20744,7 +20749,7 @@
         <v>20</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>20</v>
@@ -20755,14 +20760,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20784,10 +20789,10 @@
         <v>138</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>141</v>
@@ -20842,7 +20847,7 @@
         <v>20</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20877,10 +20882,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20906,16 +20911,16 @@
         <v>203</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>20</v>
@@ -20940,13 +20945,13 @@
         <v>20</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>295</v>
+        <v>623</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>20</v>
@@ -20964,7 +20969,7 @@
         <v>20</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>92</v>
@@ -20982,16 +20987,16 @@
         <v>20</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>622</v>
+        <v>301</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>623</v>
+        <v>302</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>20</v>
@@ -20999,10 +21004,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21025,13 +21030,13 @@
         <v>20</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21082,7 +21087,7 @@
         <v>20</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21106,7 +21111,7 @@
         <v>20</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>20</v>
@@ -21117,10 +21122,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21149,7 +21154,7 @@
         <v>139</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N153" t="s" s="2">
         <v>141</v>
@@ -21190,10 +21195,10 @@
         <v>20</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>20</v>
@@ -21202,7 +21207,7 @@
         <v>198</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21226,7 +21231,7 @@
         <v>20</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>20</v>
@@ -21237,10 +21242,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21263,19 +21268,19 @@
         <v>93</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>20</v>
@@ -21324,7 +21329,7 @@
         <v>20</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21345,10 +21350,10 @@
         <v>20</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>20</v>
@@ -21359,10 +21364,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21385,13 +21390,13 @@
         <v>20</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21442,7 +21447,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21466,7 +21471,7 @@
         <v>20</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>20</v>
@@ -21477,10 +21482,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21509,7 +21514,7 @@
         <v>139</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>141</v>
@@ -21550,10 +21555,10 @@
         <v>20</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>20</v>
@@ -21562,7 +21567,7 @@
         <v>198</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21586,7 +21591,7 @@
         <v>20</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>20</v>
@@ -21597,10 +21602,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21626,16 +21631,16 @@
         <v>106</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>20</v>
@@ -21645,7 +21650,7 @@
         <v>20</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>20</v>
@@ -21684,7 +21689,7 @@
         <v>20</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21705,10 +21710,10 @@
         <v>20</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>20</v>
@@ -21719,10 +21724,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21745,16 +21750,16 @@
         <v>93</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -21804,7 +21809,7 @@
         <v>20</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21825,10 +21830,10 @@
         <v>20</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>20</v>
@@ -21839,10 +21844,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21868,14 +21873,14 @@
         <v>112</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>20</v>
@@ -21885,7 +21890,7 @@
         <v>20</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>20</v>
@@ -21924,7 +21929,7 @@
         <v>20</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21945,10 +21950,10 @@
         <v>20</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>20</v>
@@ -21959,10 +21964,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21985,17 +21990,17 @@
         <v>93</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>20</v>
@@ -22005,7 +22010,7 @@
         <v>20</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>20</v>
@@ -22044,7 +22049,7 @@
         <v>20</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -22065,10 +22070,10 @@
         <v>20</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>20</v>
@@ -22079,10 +22084,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22105,19 +22110,19 @@
         <v>93</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -22166,7 +22171,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -22187,10 +22192,10 @@
         <v>20</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>20</v>
@@ -22201,10 +22206,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22227,19 +22232,19 @@
         <v>93</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>20</v>
@@ -22288,7 +22293,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22309,10 +22314,10 @@
         <v>20</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>20</v>
@@ -22323,10 +22328,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22349,19 +22354,19 @@
         <v>93</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>439</v>
+        <v>628</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>20</v>
@@ -22410,7 +22415,7 @@
         <v>20</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22428,27 +22433,27 @@
         <v>20</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22474,16 +22479,16 @@
         <v>203</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>20</v>
@@ -22508,13 +22513,13 @@
         <v>20</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>20</v>
@@ -22532,7 +22537,7 @@
         <v>20</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22541,7 +22546,7 @@
         <v>92</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>104</v>
@@ -22556,7 +22561,7 @@
         <v>135</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>20</v>
@@ -22567,14 +22572,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -22596,16 +22601,16 @@
         <v>203</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>20</v>
@@ -22630,13 +22635,13 @@
         <v>20</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>20</v>
@@ -22654,7 +22659,7 @@
         <v>20</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22672,27 +22677,27 @@
         <v>20</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22718,16 +22723,16 @@
         <v>82</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>20</v>
@@ -22776,7 +22781,7 @@
         <v>20</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22797,10 +22802,10 @@
         <v>20</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
+++ b/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
+++ b/docs/StructureDefinition-PASportObservationWeightTraining.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
